--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="554">
   <si>
     <t>Property</t>
   </si>
@@ -901,6 +901,9 @@
     <t>このObservationに関するLOINC上の分類、必須項目</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -934,9 +937,6 @@
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
-    <t>Dental</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.userSelected</t>
   </si>
   <si>
@@ -949,10 +949,10 @@
     <t>third</t>
   </si>
   <si>
-    <t>このObservationに関する詳細分類、JP_ObservationDentalCategory_VSより選択する、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:third.id</t>
@@ -982,13 +982,10 @@
     <t>Observation.category:third.coding.code</t>
   </si>
   <si>
-    <t>MissingToothCondition</t>
+    <t>DO-1-03</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
-  </si>
-  <si>
-    <t>Missing Tooth Condition</t>
   </si>
   <si>
     <t>Observation.category:third.coding.userSelected</t>
@@ -2080,7 +2077,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5419,11 +5416,11 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5476,7 +5473,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>202</v>
@@ -5594,7 +5591,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>209</v>
@@ -5714,7 +5711,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>215</v>
@@ -5836,7 +5833,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>225</v>
@@ -5954,7 +5951,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>227</v>
@@ -6074,7 +6071,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>229</v>
@@ -6119,7 +6116,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6196,7 +6193,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>239</v>
@@ -6316,7 +6313,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>247</v>
@@ -6359,7 +6356,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6436,7 +6433,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>256</v>
@@ -6482,7 +6479,7 @@
         <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>83</v>
@@ -7928,7 +7925,7 @@
         <v>83</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>83</v>
@@ -8002,7 +7999,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>264</v>
@@ -8124,7 +8121,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>274</v>
@@ -8246,14 +8243,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8275,16 +8272,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8309,14 +8306,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Y52" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Y52" t="s" s="2">
+      <c r="Z52" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8333,7 +8330,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8348,30 +8345,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8486,10 +8483,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8606,10 +8603,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8635,10 +8632,10 @@
         <v>216</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>219</v>
@@ -8728,10 +8725,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8846,10 +8843,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8966,10 +8963,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9011,7 +9008,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9088,10 +9085,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9208,10 +9205,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9251,7 +9248,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9328,10 +9325,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9374,7 +9371,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9448,10 +9445,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9570,10 +9567,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9692,10 +9689,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9718,19 +9715,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9779,7 +9776,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9794,19 +9791,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9814,10 +9811,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9840,7 +9837,7 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>162</v>
@@ -9849,7 +9846,7 @@
         <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9899,7 +9896,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9920,13 +9917,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9934,14 +9931,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9960,19 +9957,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10021,7 +10018,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10036,19 +10033,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10056,14 +10053,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10082,19 +10079,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10143,7 +10140,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10158,19 +10155,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10178,10 +10175,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10204,16 +10201,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10263,7 +10260,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10284,13 +10281,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10298,10 +10295,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10324,19 +10321,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10385,7 +10382,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10400,19 +10397,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10420,10 +10417,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10449,16 +10446,16 @@
         <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10507,7 +10504,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10516,7 +10513,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10525,27 +10522,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10571,16 +10568,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10605,14 +10602,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Y71" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="Z71" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10629,7 +10626,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10638,7 +10635,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10653,7 +10650,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10664,14 +10661,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10699,10 +10696,10 @@
         <v>162</v>
       </c>
       <c r="N72" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10727,14 +10724,14 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
       </c>
@@ -10751,7 +10748,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10769,27 +10766,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10812,7 +10809,7 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>162</v>
@@ -10821,10 +10818,10 @@
         <v>162</v>
       </c>
       <c r="N73" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O73" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10873,7 +10870,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10894,10 +10891,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10908,10 +10905,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10937,13 +10934,13 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10969,14 +10966,14 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10993,7 +10990,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11011,27 +11008,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11057,16 +11054,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11091,14 +11088,14 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11115,7 +11112,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11136,10 +11133,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11150,10 +11147,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11176,7 +11173,7 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>162</v>
@@ -11185,7 +11182,7 @@
         <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11235,7 +11232,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11253,27 +11250,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11296,16 +11293,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11355,7 +11352,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11373,27 +11370,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>459</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11416,7 +11413,7 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>162</v>
@@ -11425,10 +11422,10 @@
         <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11477,7 +11474,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11489,19 +11486,19 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11512,10 +11509,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11630,10 +11627,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11750,14 +11747,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11779,10 +11776,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11837,7 +11834,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11872,10 +11869,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11898,13 +11895,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11955,7 +11952,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11964,7 +11961,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -11976,10 +11973,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -11990,10 +11987,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12016,13 +12013,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12073,7 +12070,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12082,7 +12079,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12094,10 +12091,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12108,10 +12105,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12137,16 +12134,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12174,11 +12171,11 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12195,7 +12192,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12213,13 +12210,13 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AN84" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12230,10 +12227,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12259,16 +12256,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12293,14 +12290,14 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12317,7 +12314,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12335,13 +12332,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AM85" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AN85" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12352,10 +12349,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12378,17 +12375,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12437,7 +12434,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12461,7 +12458,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12472,10 +12469,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12501,10 +12498,10 @@
         <v>203</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12555,7 +12552,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12576,10 +12573,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12590,10 +12587,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12616,16 +12613,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12675,7 +12672,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12696,10 +12693,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12710,10 +12707,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12736,7 +12733,7 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>162</v>
@@ -12745,7 +12742,7 @@
         <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12795,7 +12792,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12816,10 +12813,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12830,10 +12827,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12856,19 +12853,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -12917,7 +12914,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12938,10 +12935,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12952,10 +12949,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13070,10 +13067,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13190,14 +13187,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13219,10 +13216,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13277,7 +13274,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13312,10 +13309,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13341,16 +13338,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>533</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13375,14 +13372,14 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Y94" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Y94" t="s" s="2">
+      <c r="Z94" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13399,7 +13396,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13417,16 +13414,16 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13434,10 +13431,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13460,19 +13457,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>539</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13521,7 +13518,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13539,27 +13536,27 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13585,16 +13582,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13619,14 +13616,14 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Y96" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Y96" t="s" s="2">
+      <c r="Z96" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13643,7 +13640,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13652,7 +13649,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -13667,7 +13664,7 @@
         <v>137</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13678,14 +13675,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13707,16 +13704,16 @@
         <v>188</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13741,14 +13738,14 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13765,7 +13762,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13783,27 +13780,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13829,16 +13826,16 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13887,7 +13884,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13908,10 +13905,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1454,7 +1454,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -617,7 +617,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -642,7 +645,10 @@
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -898,10 +904,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -3852,22 +3858,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>186</v>
@@ -3894,10 +3902,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3905,13 +3913,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3921,7 +3929,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3936,13 +3944,13 @@
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>191</v>
@@ -3974,7 +3982,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4016,10 +4024,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4027,10 +4035,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4053,13 +4061,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4110,7 +4118,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4134,7 +4142,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4145,10 +4153,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4177,7 +4185,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4218,19 +4226,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4254,7 +4262,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4265,10 +4273,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4291,19 +4299,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4352,7 +4360,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4373,10 +4381,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4387,10 +4395,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4413,13 +4421,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4470,7 +4478,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4494,7 +4502,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4505,10 +4513,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4537,7 +4545,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4578,19 +4586,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4614,7 +4622,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4625,10 +4633,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4654,23 +4662,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4712,7 +4720,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4733,10 +4741,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4747,10 +4755,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4773,16 +4781,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4832,7 +4840,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4853,10 +4861,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4867,10 +4875,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4896,21 +4904,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4952,7 +4960,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4973,10 +4981,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4987,10 +4995,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5013,17 +5021,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5072,7 +5080,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5093,10 +5101,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5107,10 +5115,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5133,19 +5141,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5194,7 +5202,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5215,10 +5223,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5229,10 +5237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5255,19 +5263,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5316,7 +5324,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5337,10 +5345,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5351,13 +5359,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5382,13 +5390,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>191</v>
@@ -5416,11 +5424,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5462,10 +5472,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5473,10 +5483,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5499,13 +5509,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5556,7 +5566,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5580,7 +5590,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5591,10 +5601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5623,7 +5633,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5664,19 +5674,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5700,7 +5710,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5711,10 +5721,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5737,19 +5747,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5798,7 +5808,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5819,10 +5829,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5833,10 +5843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5859,13 +5869,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5916,7 +5926,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5940,7 +5950,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5951,10 +5961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5983,7 +5993,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6024,19 +6034,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6060,7 +6070,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6071,10 +6081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6100,23 +6110,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6158,7 +6168,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6179,10 +6189,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6193,10 +6203,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6219,16 +6229,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6278,7 +6288,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6299,10 +6309,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6313,10 +6323,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6342,21 +6352,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6398,7 +6408,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6419,10 +6429,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6433,10 +6443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6459,17 +6469,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6518,7 +6528,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6539,10 +6549,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6553,10 +6563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6579,19 +6589,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6640,7 +6650,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6661,10 +6671,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6675,10 +6685,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6701,19 +6711,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6762,7 +6772,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6783,10 +6793,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6797,13 +6807,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6828,13 +6838,13 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>191</v>
@@ -6866,7 +6876,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6908,10 +6918,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6919,10 +6929,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6945,13 +6955,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7002,7 +7012,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7026,7 +7036,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7037,10 +7047,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7069,7 +7079,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7110,19 +7120,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7146,7 +7156,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7157,10 +7167,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7183,19 +7193,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7244,7 +7254,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7265,10 +7275,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7279,10 +7289,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7305,13 +7315,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7362,7 +7372,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7386,7 +7396,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7397,10 +7407,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7429,7 +7439,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7470,19 +7480,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7506,7 +7516,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7517,10 +7527,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7546,23 +7556,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7604,7 +7614,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7625,10 +7635,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7639,10 +7649,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7665,16 +7675,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7724,7 +7734,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7745,10 +7755,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7788,21 +7798,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7844,7 +7854,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7865,10 +7875,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7879,10 +7889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7905,17 +7915,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7964,7 +7974,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7985,10 +7995,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7999,10 +8009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8025,19 +8035,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8086,7 +8096,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8107,10 +8117,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8121,10 +8131,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8147,19 +8157,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8208,7 +8218,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8229,10 +8239,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8243,14 +8253,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8272,16 +8282,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8306,13 +8316,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8330,7 +8340,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8345,30 +8355,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8391,13 +8401,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8448,7 +8458,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8472,7 +8482,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8483,10 +8493,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8515,7 +8525,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8556,19 +8566,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8592,7 +8602,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8603,10 +8613,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8629,19 +8639,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8690,7 +8700,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8711,10 +8721,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8725,10 +8735,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8751,13 +8761,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8808,7 +8818,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8832,7 +8842,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8843,10 +8853,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8875,7 +8885,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8916,19 +8926,19 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8952,7 +8962,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8963,10 +8973,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8992,23 +9002,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9050,7 +9060,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9071,10 +9081,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9095,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9111,16 +9121,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9170,7 +9180,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9191,10 +9201,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9205,10 +9215,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9234,21 +9244,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9290,7 +9300,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9311,10 +9321,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9325,10 +9335,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9351,17 +9361,17 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9371,7 +9381,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9410,7 +9420,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9431,10 +9441,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9445,10 +9455,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9471,19 +9481,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9532,7 +9542,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9553,10 +9563,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9567,10 +9577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9593,19 +9603,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9654,7 +9664,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9675,10 +9685,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9689,10 +9699,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9715,19 +9725,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9776,7 +9786,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9791,19 +9801,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9811,10 +9821,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9837,7 +9847,7 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>162</v>
@@ -9846,7 +9856,7 @@
         <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9896,7 +9906,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9917,13 +9927,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9931,14 +9941,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9957,19 +9967,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10018,7 +10028,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10033,19 +10043,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10053,14 +10063,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10079,19 +10089,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10140,7 +10150,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10155,19 +10165,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10175,10 +10185,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10201,16 +10211,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10260,7 +10270,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10281,13 +10291,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10295,10 +10305,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10321,19 +10331,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10382,7 +10392,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10397,19 +10407,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10417,10 +10427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10446,16 +10456,16 @@
         <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10504,7 +10514,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10513,7 +10523,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10522,27 +10532,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10568,16 +10578,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10602,13 +10612,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10626,7 +10636,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10635,7 +10645,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10650,7 +10660,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10661,14 +10671,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10696,10 +10706,10 @@
         <v>162</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10724,13 +10734,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10748,7 +10758,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10766,27 +10776,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10809,7 +10819,7 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>162</v>
@@ -10818,10 +10828,10 @@
         <v>162</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10870,7 +10880,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10891,10 +10901,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10905,10 +10915,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10934,13 +10944,13 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10966,13 +10976,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10990,7 +11000,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11008,27 +11018,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11054,16 +11064,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11088,13 +11098,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11112,7 +11122,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11133,10 +11143,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11147,10 +11157,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11173,7 +11183,7 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>162</v>
@@ -11182,7 +11192,7 @@
         <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11232,7 +11242,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11250,27 +11260,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11293,16 +11303,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11352,7 +11362,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11370,27 +11380,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11413,7 +11423,7 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>162</v>
@@ -11422,10 +11432,10 @@
         <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11474,7 +11484,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11486,7 +11496,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11495,10 +11505,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11509,10 +11519,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11535,13 +11545,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11592,7 +11602,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11616,7 +11626,7 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11627,10 +11637,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11659,7 +11669,7 @@
         <v>141</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>143</v>
@@ -11712,7 +11722,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11736,7 +11746,7 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11747,14 +11757,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11776,10 +11786,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11834,7 +11844,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11869,10 +11879,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11895,13 +11905,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11952,7 +11962,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11961,7 +11971,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -11973,10 +11983,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -11987,10 +11997,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12013,13 +12023,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12070,7 +12080,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12079,7 +12089,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12091,10 +12101,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12105,10 +12115,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12134,16 +12144,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12171,10 +12181,10 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12192,7 +12202,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12210,13 +12220,13 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12227,10 +12237,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12256,16 +12266,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12290,13 +12300,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12314,7 +12324,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12332,13 +12342,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12349,10 +12359,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12375,17 +12385,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12434,7 +12444,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12458,7 +12468,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12469,10 +12479,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12495,13 +12505,13 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12552,7 +12562,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12573,10 +12583,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12587,10 +12597,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12613,16 +12623,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12672,7 +12682,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12693,10 +12703,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12707,10 +12717,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12733,7 +12743,7 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>162</v>
@@ -12742,7 +12752,7 @@
         <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12792,7 +12802,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12813,10 +12823,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12827,10 +12837,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12853,19 +12863,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -12914,7 +12924,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12935,10 +12945,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12949,10 +12959,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12975,13 +12985,13 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13032,7 +13042,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13056,7 +13066,7 @@
         <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13067,10 +13077,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13099,7 +13109,7 @@
         <v>141</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>143</v>
@@ -13152,7 +13162,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13176,7 +13186,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13187,14 +13197,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13216,10 +13226,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13274,7 +13284,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13309,10 +13319,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13338,16 +13348,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13372,13 +13382,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13396,7 +13406,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13414,16 +13424,16 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13431,10 +13441,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13457,19 +13467,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13518,7 +13528,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13536,27 +13546,27 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13582,16 +13592,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13616,13 +13626,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -13640,7 +13650,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13649,7 +13659,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -13664,7 +13674,7 @@
         <v>137</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13675,14 +13685,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13704,16 +13714,16 @@
         <v>188</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13738,13 +13748,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13762,7 +13772,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13780,27 +13790,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13826,16 +13836,16 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13884,7 +13894,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13905,10 +13915,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -1358,10 +1358,7 @@
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -10978,11 +10975,9 @@
       <c r="X74" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y74" t="s" s="2">
+      <c r="Y74" s="2"/>
+      <c r="Z74" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11018,27 +11013,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>437</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11064,16 +11059,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11101,11 +11096,11 @@
         <v>323</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11122,7 +11117,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11143,10 +11138,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11157,10 +11152,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11183,7 +11178,7 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>162</v>
@@ -11192,7 +11187,7 @@
         <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11242,7 +11237,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11260,27 +11255,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11303,16 +11298,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11362,7 +11357,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11380,27 +11375,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>460</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11423,7 +11418,7 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>162</v>
@@ -11432,10 +11427,10 @@
         <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O78" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11484,7 +11479,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11496,19 +11491,19 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11519,10 +11514,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11637,10 +11632,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11757,14 +11752,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11786,10 +11781,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11844,7 +11839,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11879,10 +11874,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11905,13 +11900,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11962,7 +11957,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11971,7 +11966,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -11983,10 +11978,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -11997,10 +11992,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12023,13 +12018,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12080,7 +12075,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12089,7 +12084,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12101,10 +12096,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12115,10 +12110,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12144,16 +12139,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12181,11 +12176,11 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12202,7 +12197,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12220,10 +12215,10 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>421</v>
@@ -12237,10 +12232,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12266,16 +12261,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12303,11 +12298,11 @@
         <v>323</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12324,7 +12319,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12342,10 +12337,10 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>421</v>
@@ -12359,10 +12354,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12385,17 +12380,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12444,7 +12439,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12468,7 +12463,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12479,10 +12474,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12508,10 +12503,10 @@
         <v>205</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12562,7 +12557,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12583,10 +12578,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12597,10 +12592,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12623,16 +12618,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12682,7 +12677,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12703,10 +12698,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12717,10 +12712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12743,7 +12738,7 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>162</v>
@@ -12752,7 +12747,7 @@
         <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12802,7 +12797,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12823,10 +12818,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12837,10 +12832,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12863,19 +12858,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -12924,7 +12919,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12945,10 +12940,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12959,10 +12954,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13077,10 +13072,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13197,14 +13192,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13226,10 +13221,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13284,7 +13279,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13319,10 +13314,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13348,13 +13343,13 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>322</v>
@@ -13406,7 +13401,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13424,7 +13419,7 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>328</v>
@@ -13441,10 +13436,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13467,16 +13462,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>398</v>
@@ -13528,7 +13523,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13546,7 +13541,7 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>401</v>
@@ -13563,10 +13558,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13592,13 +13587,13 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>407</v>
@@ -13650,7 +13645,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13685,10 +13680,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13714,16 +13709,16 @@
         <v>188</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13772,7 +13767,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13807,10 +13802,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13836,16 +13831,16 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13894,7 +13889,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13915,10 +13910,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -904,7 +904,7 @@
     <t>second</t>
   </si>
   <si>
-    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1283,7 +1283,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1458,7 +1458,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1717,7 +1717,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2079,7 +2079,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -1529,7 +1529,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4825" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -608,9 +608,9 @@
     <t>このObservationを分類するコード</t>
   </si>
   <si>
-    <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
-第2コード（second）は、歯科を表すコードLP89803-8を設定する。
+    <t>3つのコードを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
+第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
   <si>
@@ -1353,8 +1353,8 @@
     <t>特定の歯（歯式）</t>
   </si>
   <si>
-    <t>優先順位は以下の番号を推奨する。
-1.FDI
+    <t>優先順位は以下の番号を推奨する。
+1.FDI
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
@@ -1679,13 +1679,122 @@
     <t>観察されたものについて説明します。これは、「コード」と呼ばれることがあります。 / Describes what was observed. Sometimes this is called the observation "code".</t>
   </si>
   <si>
-    <t>2つのいずれかのコードを設定する。
-主コード（primary）は、細かい粒度の欠損歯の処置状態
+    <t>2つのいずれかのコードを設定する。
+主コード（primary）は、細かい粒度の欠損歯の処置状態
 副コード（sub）は、粗い粒度の欠損歯の処置状態</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>細かい粒度の欠損歯の処置状態</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalMissingTeethObservation_VS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalMissingTeethObservation_CS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:primary.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>粗い粒度の欠損歯の処置状態</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSimpleMissingTeethObservation_VS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSimpleMissingTeethObservation_CS</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding:sub.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -2052,11 +2161,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP98"/>
+  <dimension ref="A1:AP125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.19921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2080,7 +2189,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.8671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -13459,23 +13568,19 @@
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>536</v>
+        <v>205</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>537</v>
+        <v>206</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13523,7 +13628,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>535</v>
+        <v>208</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13535,44 +13640,44 @@
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>540</v>
+        <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>402</v>
+        <v>209</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -13584,20 +13689,18 @@
         <v>83</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>542</v>
+        <v>141</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>543</v>
+        <v>212</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13621,43 +13724,43 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>541</v>
+        <v>215</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>83</v>
@@ -13666,10 +13769,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>412</v>
+        <v>209</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13680,14 +13783,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13703,22 +13806,22 @@
         <v>83</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>546</v>
+        <v>219</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>547</v>
+        <v>220</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>548</v>
+        <v>221</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>549</v>
+        <v>222</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13743,31 +13846,29 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>545</v>
+        <v>223</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13785,27 +13886,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>420</v>
+        <v>224</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>421</v>
+        <v>225</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13816,7 +13917,7 @@
         <v>81</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>83</v>
@@ -13828,20 +13929,16 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>551</v>
+        <v>206</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -13889,36 +13986,3298 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y105" s="2"/>
+      <c r="Z105" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
+      <c r="B106" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G107" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
+      <c r="H107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AK108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y113" s="2"/>
+      <c r="Z113" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN98" t="s" s="2">
+      <c r="AN125" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AO98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP98" t="s" s="2">
+      <c r="AO125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP125" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -2164,15 +2164,15 @@
   <dimension ref="A1:AP125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.19921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.32421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2183,28 +2183,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.8671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.47265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -609,7 +609,7 @@
   </si>
   <si>
     <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
+第1コード（first）は、simpleObservationコード体系を必須とし、examを設定する。
 第2コード（second）は、歯科を表すコードLP89803-8を設定する。
 第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
   </si>
@@ -804,7 +804,7 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>procedure</t>
+    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2024-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4825" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4826" uniqueCount="592">
   <si>
     <t>Property</t>
   </si>
@@ -1358,7 +1358,10 @@
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -11084,9 +11087,11 @@
       <c r="X74" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y74" s="2"/>
+      <c r="Y74" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11122,27 +11127,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11168,16 +11173,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11205,10 +11210,10 @@
         <v>323</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11226,7 +11231,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11247,10 +11252,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11261,10 +11266,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11287,7 +11292,7 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>162</v>
@@ -11296,7 +11301,7 @@
         <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11346,7 +11351,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11364,27 +11369,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11407,16 +11412,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11466,7 +11471,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11484,27 +11489,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11527,7 +11532,7 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>162</v>
@@ -11536,10 +11541,10 @@
         <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11588,7 +11593,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11600,7 +11605,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11609,10 +11614,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11623,10 +11628,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11741,10 +11746,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11861,14 +11866,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11890,10 +11895,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11948,7 +11953,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11983,10 +11988,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12009,13 +12014,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12066,7 +12071,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12075,7 +12080,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -12087,10 +12092,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12101,10 +12106,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12127,13 +12132,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12184,7 +12189,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12193,7 +12198,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12205,10 +12210,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12219,10 +12224,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12248,16 +12253,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12285,10 +12290,10 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12306,7 +12311,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12324,10 +12329,10 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>421</v>
@@ -12341,10 +12346,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12370,16 +12375,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12407,10 +12412,10 @@
         <v>323</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12428,7 +12433,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12446,10 +12451,10 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>421</v>
@@ -12463,10 +12468,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12489,17 +12494,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12548,7 +12553,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12572,7 +12577,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12583,10 +12588,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12612,10 +12617,10 @@
         <v>205</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12666,7 +12671,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12687,10 +12692,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12701,10 +12706,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12727,16 +12732,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12786,7 +12791,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12807,10 +12812,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12821,10 +12826,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12847,7 +12852,7 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>162</v>
@@ -12856,7 +12861,7 @@
         <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12906,7 +12911,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12927,10 +12932,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12941,10 +12946,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12967,19 +12972,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13028,7 +13033,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13049,10 +13054,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13063,10 +13068,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13181,10 +13186,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13301,14 +13306,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13330,10 +13335,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13388,7 +13393,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13423,10 +13428,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13452,13 +13457,13 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>322</v>
@@ -13510,7 +13515,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13528,7 +13533,7 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>328</v>
@@ -13545,10 +13550,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13663,10 +13668,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13783,10 +13788,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13858,7 +13863,7 @@
         <v>83</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
@@ -13903,10 +13908,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14021,10 +14026,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14141,10 +14146,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14263,10 +14268,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14383,10 +14388,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14503,10 +14508,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14623,10 +14628,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14745,13 +14750,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>83</v>
@@ -14776,10 +14781,10 @@
         <v>218</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>221</v>
@@ -14814,7 +14819,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
@@ -14867,10 +14872,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14985,10 +14990,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15105,10 +15110,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15150,7 +15155,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>83</v>
@@ -15227,10 +15232,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15347,10 +15352,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15467,10 +15472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15587,10 +15592,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15709,13 +15714,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>83</v>
@@ -15740,10 +15745,10 @@
         <v>218</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>221</v>
@@ -15778,7 +15783,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -15831,10 +15836,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15949,10 +15954,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16069,10 +16074,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16114,7 +16119,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>83</v>
@@ -16191,10 +16196,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16311,10 +16316,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16431,10 +16436,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16551,10 +16556,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16673,10 +16678,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16795,10 +16800,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16821,16 +16826,16 @@
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>398</v>
@@ -16882,7 +16887,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16900,7 +16905,7 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>401</v>
@@ -16917,10 +16922,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16946,13 +16951,13 @@
         <v>188</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>407</v>
@@ -17004,7 +17009,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17039,10 +17044,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17068,16 +17073,16 @@
         <v>188</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17126,7 +17131,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17161,10 +17166,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17190,16 +17195,16 @@
         <v>84</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -17248,7 +17253,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -17269,10 +17274,10 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4826" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -492,7 +492,11 @@
 </t>
   </si>
   <si>
-    <t>当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。例えば、実施日に連番を付加した番号など。</t>
+    <t>Observationのためのビジネス識別子  
+【JP Core仕様】当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。</t>
+  </si>
+  <si>
+    <t>例：実施日に連番を付加した番号</t>
   </si>
   <si>
     <t>観測を区別し、参照することを可能にします。 / Allows observations to be distinguished and referenced.</t>
@@ -521,7 +525,11 @@
 </t>
   </si>
   <si>
-    <t>未使用</t>
+    <t>実施されるプラン、提案、依頼  
+【JP Core仕様】未使用</t>
+  </si>
+  <si>
+    <t>本プロファイル（特定の歯の有無・状態）は口腔診査レポートに紐付く前提のため、本プロファイル特有の定義はしない。</t>
   </si>
   <si>
     <t>イベントの許可を追跡し、提案/勧告が行われたかどうかを追跡することができます。 / Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -547,6 +555,10 @@
 </t>
   </si>
   <si>
+    <t>参照されるイベントの一部分  
+【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>ObservationをEncounterにencounter要素を使ってリンクする。もうひとつ別のObservationを参照することについては、以降にあるt [Notes](observation.html#obsgrouping)　をガイダンスとして参照のこと。</t>
   </si>
   <si>
@@ -562,7 +574,8 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>結果の状態</t>
+    <t>結果の状態  
+【JP Core仕様】ステータス</t>
   </si>
   <si>
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
@@ -605,13 +618,14 @@
 </t>
   </si>
   <si>
-    <t>このObservationを分類するコード</t>
-  </si>
-  <si>
-    <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、examを設定する。
-第2コード（second）は、歯科を表すコードLP89803-8を設定する。
-第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
+    <t>Observationの種類（タイプ）の分類
+【JP Core仕様】以下を指定する。
+第1コード：exam
+第2コード：LP89803-8 （Dental）
+第3コード：DO-1-03 （MissingToothCondition）</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
@@ -907,9 +921,6 @@
     <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
-  </si>
-  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -1052,7 +1063,8 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>このObservationの対象を特定するコード。LOINCより歯の有無・状態を表す54570-7を選択する。</t>
+    <t>observation のタイプ（コードまたはタイプ）
+【JP Core仕様】54570-7（Oral/dental status）を指定する</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
@@ -1092,7 +1104,7 @@
 </t>
   </si>
   <si>
-    <t>患者情報</t>
+    <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
     <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
@@ -1120,6 +1132,9 @@
 </t>
   </si>
   <si>
+    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。  【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
@@ -1137,10 +1152,10 @@
 </t>
   </si>
   <si>
-    <t>例：診療、歯科健診（検診）、身元不明者調査</t>
-  </si>
-  <si>
-    <t>通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
+    <t>このobservationが行われるヘルスケアイベント</t>
+  </si>
+  <si>
+    <t>例：診療、歯科検診、身元不明者調査</t>
   </si>
   <si>
     <t>一部の観察では、観察と特定のEncounterの間のリンクを知ることが重要かもしれません。 / For some observations it may be important to know the link between an observation and a particular encounter.</t>
@@ -1169,7 +1184,7 @@
 </t>
   </si>
   <si>
-    <t>実施日時</t>
+    <t>臨床的に関連する時刻または時間  【JP Core仕様】実施日時</t>
   </si>
   <si>
     <t>この観察結果が過去の報告でない限り、少なくとも日付が存在する必要がある。不正確または「あいまいな」時間を記録するには（たとえば、「朝食後」に行われた血糖測定）、[Timing]（datatypes.html＃timing）データ型を使用して、測定を通常のライフイベントに関連付けることができる。</t>
@@ -1197,7 +1212,7 @@
 </t>
   </si>
   <si>
-    <t>所見確定日時</t>
+    <t>このバージョンが利用可能となった日時  【JP Core仕様】所見確定日時</t>
   </si>
   <si>
     <t>レビューと検証を必要としないobservationの場合、リソース自体の[`lastUpdated`]（resource-definitions.html＃Meta.lastUpdated）日時と同じになる場合がある。特定の更新のレビューと検証が必要なobservationの場合、新しいバージョンを再度レビューして検証する必要がないような臨床的に重要でない更新がなされたために、リソース自体の「lastUpdated」時間はこれと異なる場合がある。</t>
@@ -1219,12 +1234,12 @@
 </t>
   </si>
   <si>
+    <t>observationに責任をもつ者</t>
+  </si>
+  <si>
     <t>例：歯科医師など</t>
   </si>
   <si>
-    <t>参照は、実際のFHIRリソースへの参照である必要があり、解決可能（内容に到達可能）である必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
-  </si>
-  <si>
     <t>観察にある程度の自信を与える可能性があり、また、フォローアップの質問をどこに向けるべきかを示します。 / May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
@@ -1243,10 +1258,10 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>使用しない</t>
-  </si>
-  <si>
-    <t>日本仕様ではComponent要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない。</t>
+    <t>実際の結果値  【JP Core仕様】component要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない</t>
+  </si>
+  <si>
+    <t>観察にはあります。1）ここでの単一の値、2）関連する値とコンポーネント値のセット、または3）関連またはコンポーネント値のセットのみ。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1271,7 +1286,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>結果が存在しなかった場合、その理由</t>
+    <t>結果が欠損値である理由  【JP Core仕様】結果が存在しなかった場合、その理由</t>
   </si>
   <si>
     <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
@@ -1303,6 +1318,9 @@
 </t>
   </si>
   <si>
+    <t>高、低、正常等の結果のカテゴリ分けした評価【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>「異常フラグ」として呼ばれる検査結果解釈コードが従来から使用されており、その使用はコード化された解釈が関連するような他の場合でも拡大して使われている。多くの場合、1つ以上の単純でコンパクトなコードとして報告され、この要素は、結果の意味や正常かどうかを示すために、レポートや時系列表で結果値の隣に配置されることがよくある。</t>
   </si>
   <si>
@@ -1334,6 +1352,9 @@
 </t>
   </si>
   <si>
+    <t>結果に対するコメント  【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>観察（結果）に関する一般的な記述、重要な、予期しない、または信頼できない結果値に関する記述、またはその解釈に関連する場合はそのソースに関する情報が含まれる場合がある。</t>
   </si>
   <si>
@@ -1350,18 +1371,15 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>特定の歯（歯式）</t>
-  </si>
-  <si>
-    <t>優先順位は以下の番号を推奨する。
-1.FDI
-2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
-  </si>
-  <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>観察された身体部位  【JP Core仕様】特定の歯（歯式）を指定</t>
+  </si>
+  <si>
+    <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
+ユースケースでは、ボディサイトを個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalBodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1374,6 +1392,44 @@
   </si>
   <si>
     <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.id</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:toothRoot</t>
+  </si>
+  <si>
+    <t>toothRoot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_ToothRoot}
+</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】特定の歯の歯根を指定</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:toothSurface</t>
+  </si>
+  <si>
+    <t>toothSurface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_ToothSurface}
+</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】特定の歯の歯面を指定</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.coding</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.text</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -1407,6 +1463,9 @@
 </t>
   </si>
   <si>
+    <t>観察（観測、検査）に使われた検体材料 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
   </si>
   <si>
@@ -1429,10 +1488,10 @@
 </t>
   </si>
   <si>
+    <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
+  </si>
+  <si>
     <t>例：口腔内スキャナなど</t>
-  </si>
-  <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -1452,6 +1511,9 @@
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
+  </si>
+  <si>
+    <t>基準範囲との比較による結果の解釈方法のガイダンス</t>
   </si>
   <si>
     <t>通常の範囲または推奨範囲と比較して値を解釈する方法に関するガイダンス。複数の参照範囲は「OR」として解釈される。つまり、2つの異なるターゲット母集団を表すために、2つの `referenceRange`要素が使用される。</t>
@@ -1617,11 +1679,11 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
-    <t>このObservationに関連する子リソースに関する情報。このObservationに関連する/属するパネル検査や検査セットなどのObservationグループ</t>
+    <t>observationグループに属する関連リソース 【JP Core仕様】欠損歯の処置状態は最終的な観察結果のため、他のObservationリソースを参照しない</t>
   </si>
   <si>
     <t>この要素を使用する場合、observationには通常、値または関連するリソースのセットのいずれかを含む。その両方を含む場合もある。複数のobservationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照せよ。システムは、[QuestionnaireResponse]（questionnaireresponse.html）からの結果を計算して最終スコアにし、そのスコアをobservationとして表す場合があることに注意。</t>
@@ -1640,6 +1702,9 @@
 </t>
   </si>
   <si>
+    <t>observationの発生源に関連する測定 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>この要素にリストされているすべての参照の選択肢は、派生値の元のデータなる可能性のある臨床観察やその他の測定値を表すことができる。最も一般的な参照先は、別のobservationである。observationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照すること。</t>
   </si>
   <si>
@@ -1649,7 +1714,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>欠損歯の処置状態</t>
+    <t>複合的な結果 【JP Core仕様】欠損歯の処置状態</t>
   </si>
   <si>
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
@@ -2164,12 +2229,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP125"/>
+  <dimension ref="A1:AP131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.32421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3431,7 +3496,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>82</v>
@@ -3454,9 +3519,11 @@
       <c r="M11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>83</v>
@@ -3520,19 +3587,19 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>83</v>
@@ -3540,14 +3607,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3566,17 +3633,19 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>83</v>
@@ -3625,7 +3694,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3640,16 +3709,16 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>83</v>
@@ -3660,14 +3729,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3686,16 +3755,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3745,7 +3814,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3760,16 +3829,16 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>83</v>
@@ -3780,10 +3849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3809,16 +3878,16 @@
         <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>83</v>
@@ -3843,13 +3912,13 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>83</v>
@@ -3867,7 +3936,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>94</v>
@@ -3882,19 +3951,19 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>83</v>
@@ -3902,10 +3971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3913,7 +3982,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
@@ -3928,19 +3997,19 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -3968,26 +4037,26 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4011,10 +4080,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -4022,13 +4091,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -4050,19 +4119,19 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -4087,11 +4156,11 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4109,7 +4178,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4133,10 +4202,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4144,10 +4213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4170,13 +4239,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4227,7 +4296,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4251,7 +4320,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4262,10 +4331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4294,7 +4363,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4335,19 +4404,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4371,7 +4440,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4382,10 +4451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4408,19 +4477,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4469,7 +4538,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4490,10 +4559,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4504,10 +4573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4530,13 +4599,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4587,7 +4656,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4611,7 +4680,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4622,10 +4691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4654,7 +4723,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4695,19 +4764,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4731,7 +4800,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4742,10 +4811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4771,23 +4840,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4829,7 +4898,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4850,10 +4919,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4864,10 +4933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4890,16 +4959,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4949,7 +5018,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4970,10 +5039,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4984,10 +5053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5013,21 +5082,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5069,7 +5138,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5090,10 +5159,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5104,10 +5173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5130,17 +5199,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5189,7 +5258,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5210,10 +5279,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5224,10 +5293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5250,19 +5319,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5311,7 +5380,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5332,10 +5401,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5346,10 +5415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5372,19 +5441,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5433,7 +5502,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5454,10 +5523,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5468,13 +5537,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5496,19 +5565,19 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>193</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5536,10 +5605,10 @@
         <v>118</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5557,7 +5626,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5581,10 +5650,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5592,10 +5661,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5618,13 +5687,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5675,7 +5744,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5699,7 +5768,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5710,10 +5779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5742,7 +5811,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5783,19 +5852,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5819,7 +5888,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5830,10 +5899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5856,19 +5925,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5917,7 +5986,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5938,10 +6007,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5952,10 +6021,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5978,13 +6047,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6035,7 +6104,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6059,7 +6128,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6070,10 +6139,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6102,7 +6171,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6143,19 +6212,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6179,7 +6248,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6190,10 +6259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6219,23 +6288,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6277,7 +6346,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6298,10 +6367,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6312,10 +6381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6338,16 +6407,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6397,7 +6466,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6418,10 +6487,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6432,10 +6501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6461,21 +6530,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6517,7 +6586,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6538,10 +6607,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6552,10 +6621,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6578,17 +6647,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6637,7 +6706,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6658,10 +6727,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6672,10 +6741,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6698,19 +6767,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6759,7 +6828,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6780,10 +6849,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6794,10 +6863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6820,19 +6889,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6881,7 +6950,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6902,10 +6971,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6916,13 +6985,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6944,19 +7013,19 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>287</v>
+        <v>193</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6981,11 +7050,11 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7003,7 +7072,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7027,10 +7096,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7038,10 +7107,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7064,13 +7133,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7121,7 +7190,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7145,7 +7214,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7156,10 +7225,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7188,7 +7257,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7229,19 +7298,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7265,7 +7334,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7276,10 +7345,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7302,19 +7371,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7363,7 +7432,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7384,10 +7453,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7398,10 +7467,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7424,13 +7493,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7481,7 +7550,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7505,7 +7574,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7516,10 +7585,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7548,7 +7617,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7589,19 +7658,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7625,7 +7694,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7636,10 +7705,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7665,23 +7734,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7723,7 +7792,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7744,10 +7813,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7758,10 +7827,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7784,16 +7853,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7843,7 +7912,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7864,10 +7933,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7878,10 +7947,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7907,21 +7976,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7963,7 +8032,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7984,10 +8053,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7998,10 +8067,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8024,17 +8093,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8083,7 +8152,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8104,10 +8173,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8118,10 +8187,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8144,19 +8213,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8205,7 +8274,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8226,10 +8295,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8240,10 +8309,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8266,19 +8335,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8327,7 +8396,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8348,10 +8417,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8362,14 +8431,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8388,19 +8457,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8425,13 +8494,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8449,7 +8518,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8464,30 +8533,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8510,13 +8579,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8567,7 +8636,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8591,7 +8660,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8602,10 +8671,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8634,7 +8703,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8675,19 +8744,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8711,7 +8780,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8722,10 +8791,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8748,19 +8817,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8809,7 +8878,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8830,10 +8899,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8844,10 +8913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8870,13 +8939,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8927,7 +8996,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8951,7 +9020,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8962,10 +9031,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8994,7 +9063,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9035,19 +9104,19 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9071,7 +9140,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9082,10 +9151,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9111,23 +9180,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9169,7 +9238,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9190,10 +9259,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9204,10 +9273,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9230,16 +9299,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9289,7 +9358,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9310,10 +9379,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9324,10 +9393,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9353,21 +9422,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9409,7 +9478,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9430,10 +9499,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9444,10 +9513,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9470,17 +9539,17 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9490,7 +9559,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9529,7 +9598,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9550,10 +9619,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9564,10 +9633,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9590,19 +9659,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9651,7 +9720,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9672,10 +9741,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9686,10 +9755,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9712,19 +9781,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9773,7 +9842,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9794,10 +9863,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9808,10 +9877,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9819,7 +9888,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>94</v>
@@ -9834,19 +9903,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9895,7 +9964,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9910,19 +9979,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9930,10 +9999,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9956,16 +10025,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>162</v>
+        <v>359</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>162</v>
+        <v>359</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10015,7 +10084,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10036,13 +10105,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10050,14 +10119,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10076,19 +10145,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10137,7 +10206,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10152,19 +10221,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10172,14 +10241,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10198,19 +10267,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10259,7 +10328,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10274,19 +10343,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10294,10 +10363,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10320,16 +10389,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10379,7 +10448,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10400,13 +10469,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10414,10 +10483,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10440,19 +10509,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10501,7 +10570,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10516,19 +10585,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10536,10 +10605,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10562,19 +10631,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10623,7 +10692,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10632,7 +10701,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10641,27 +10710,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10684,19 +10753,19 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10721,13 +10790,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10745,7 +10814,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10754,7 +10823,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10769,7 +10838,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10780,14 +10849,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10806,19 +10875,19 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>162</v>
+        <v>418</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>162</v>
+        <v>418</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10843,13 +10912,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10867,7 +10936,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10885,27 +10954,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10928,19 +10997,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>162</v>
+        <v>429</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>162</v>
+        <v>429</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10989,7 +11058,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11010,10 +11079,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11024,10 +11093,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11050,16 +11119,16 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11085,13 +11154,11 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11109,7 +11176,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11127,27 +11194,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11170,20 +11237,16 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>209</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>83</v>
       </c>
@@ -11207,13 +11270,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11231,7 +11294,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>211</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11243,7 +11306,7 @@
         <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>83</v>
@@ -11252,10 +11315,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>445</v>
+        <v>212</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11266,21 +11329,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11292,16 +11355,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>447</v>
+        <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>448</v>
+        <v>143</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11339,59 +11402,61 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>218</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>449</v>
+        <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>451</v>
+        <v>212</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
       </c>
@@ -11400,7 +11465,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11412,17 +11477,15 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11471,47 +11534,49 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>453</v>
+        <v>218</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11532,20 +11597,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>162</v>
+        <v>451</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11593,7 +11654,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>461</v>
+        <v>218</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11605,7 +11666,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>465</v>
+        <v>145</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11614,10 +11675,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11628,10 +11689,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11642,7 +11703,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11651,19 +11712,23 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11711,19 +11776,19 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11732,10 +11797,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11746,21 +11811,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
@@ -11769,21 +11834,23 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
       </c>
@@ -11831,19 +11898,19 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -11852,10 +11919,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11866,45 +11933,45 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>471</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>143</v>
+        <v>456</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>149</v>
+        <v>457</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11929,13 +11996,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>458</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -11953,19 +12020,19 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>83</v>
@@ -11974,10 +12041,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>137</v>
+        <v>461</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -11988,10 +12055,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12014,15 +12081,17 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12071,7 +12140,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12080,7 +12149,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -12089,27 +12158,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>83</v>
+        <v>466</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12132,15 +12201,17 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12189,7 +12260,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12198,7 +12269,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12207,27 +12278,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>83</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12238,7 +12309,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12250,19 +12321,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>188</v>
+        <v>479</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12287,13 +12358,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>491</v>
+        <v>83</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>492</v>
+        <v>83</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12311,31 +12382,31 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>106</v>
+        <v>483</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>493</v>
+        <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>421</v>
+        <v>485</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12346,10 +12417,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12360,7 +12431,7 @@
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>83</v>
@@ -12372,20 +12443,16 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>496</v>
+        <v>209</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12409,13 +12476,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>501</v>
+        <v>83</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12433,31 +12500,31 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>495</v>
+        <v>211</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>493</v>
+        <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>494</v>
+        <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>421</v>
+        <v>212</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12468,21 +12535,21 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>83</v>
@@ -12494,18 +12561,18 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>503</v>
+        <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>504</v>
+        <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12553,19 +12620,19 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>218</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12577,7 +12644,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>507</v>
+        <v>212</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12588,42 +12655,46 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12671,19 +12742,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12692,10 +12763,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>511</v>
+        <v>137</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12706,10 +12777,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12720,7 +12791,7 @@
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
@@ -12729,20 +12800,18 @@
         <v>83</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12791,16 +12860,16 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>83</v>
+        <v>497</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12812,10 +12881,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12826,10 +12895,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12840,7 +12909,7 @@
         <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -12849,20 +12918,18 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>162</v>
+        <v>501</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12911,16 +12978,16 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>83</v>
+        <v>497</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12932,10 +12999,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12946,10 +13013,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12960,7 +13027,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -12969,22 +13036,22 @@
         <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>462</v>
+        <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13009,13 +13076,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13033,13 +13100,13 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
@@ -13051,13 +13118,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>83</v>
+        <v>511</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>527</v>
+        <v>425</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13068,10 +13135,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13082,7 +13149,7 @@
         <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>83</v>
@@ -13094,16 +13161,20 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>206</v>
+        <v>514</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13127,13 +13198,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>518</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13151,31 +13222,31 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>208</v>
+        <v>513</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>511</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>209</v>
+        <v>425</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13186,21 +13257,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>83</v>
@@ -13212,18 +13283,18 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>140</v>
+        <v>521</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>141</v>
+        <v>522</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13271,19 +13342,19 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>215</v>
+        <v>520</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
@@ -13295,7 +13366,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>209</v>
+        <v>525</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13306,46 +13377,42 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>471</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13393,19 +13460,19 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>474</v>
+        <v>526</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>83</v>
@@ -13414,10 +13481,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>83</v>
+        <v>498</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>137</v>
+        <v>529</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13428,10 +13495,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13439,10 +13506,10 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13454,20 +13521,18 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>188</v>
+        <v>531</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>532</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -13491,13 +13556,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13515,13 +13580,13 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>83</v>
@@ -13533,16 +13598,16 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AM94" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AO94" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13564,7 +13629,7 @@
         <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13573,18 +13638,20 @@
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>205</v>
+        <v>537</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>206</v>
+        <v>538</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13633,19 +13700,19 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>208</v>
+        <v>536</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>83</v>
@@ -13654,10 +13721,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>83</v>
+        <v>534</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>209</v>
+        <v>540</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13668,14 +13735,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13691,21 +13758,23 @@
         <v>83</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>140</v>
+        <v>479</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>141</v>
+        <v>542</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>212</v>
+        <v>542</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13741,19 +13810,19 @@
         <v>83</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>215</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13765,7 +13834,7 @@
         <v>83</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>83</v>
@@ -13774,10 +13843,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>209</v>
+        <v>546</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13788,10 +13857,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13802,7 +13871,7 @@
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>83</v>
@@ -13811,23 +13880,19 @@
         <v>83</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
       </c>
@@ -13863,29 +13928,31 @@
         <v>83</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AC97" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
@@ -13894,10 +13961,10 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13908,21 +13975,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>83</v>
@@ -13934,15 +14001,17 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13991,19 +14060,19 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>83</v>
@@ -14015,7 +14084,7 @@
         <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14026,14 +14095,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>139</v>
+        <v>489</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14046,24 +14115,26 @@
         <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>141</v>
+        <v>490</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>212</v>
+        <v>491</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
       </c>
@@ -14099,19 +14170,19 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>215</v>
+        <v>492</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14135,7 +14206,7 @@
         <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>209</v>
+        <v>137</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14146,10 +14217,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14157,7 +14228,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>94</v>
@@ -14172,19 +14243,19 @@
         <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>232</v>
+        <v>551</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>233</v>
+        <v>552</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>234</v>
+        <v>553</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>235</v>
+        <v>324</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14209,13 +14280,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14233,10 +14304,10 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>237</v>
+        <v>550</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>94</v>
@@ -14251,16 +14322,16 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>83</v>
+        <v>554</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>238</v>
+        <v>330</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14268,10 +14339,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14291,20 +14362,18 @@
         <v>83</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14353,7 +14422,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14365,7 +14434,7 @@
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14374,10 +14443,10 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14388,21 +14457,21 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>83</v>
@@ -14411,21 +14480,21 @@
         <v>83</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
@@ -14461,31 +14530,31 @@
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>83</v>
@@ -14494,10 +14563,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14508,10 +14577,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14522,7 +14591,7 @@
         <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>83</v>
@@ -14534,17 +14603,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14581,25 +14652,23 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>83</v>
@@ -14614,10 +14683,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14628,10 +14697,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14651,23 +14720,19 @@
         <v>83</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>83</v>
       </c>
@@ -14715,7 +14780,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14727,7 +14792,7 @@
         <v>83</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>83</v>
@@ -14736,10 +14801,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14750,23 +14815,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>83</v>
@@ -14775,23 +14838,21 @@
         <v>83</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>549</v>
+        <v>141</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>549</v>
+        <v>215</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>83</v>
       </c>
@@ -14815,29 +14876,31 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y105" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z105" t="s" s="2">
-        <v>550</v>
+        <v>83</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14849,7 +14912,7 @@
         <v>83</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>83</v>
@@ -14858,10 +14921,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14872,10 +14935,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14895,19 +14958,23 @@
         <v>83</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>205</v>
+        <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
       </c>
@@ -14955,7 +15022,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -14967,7 +15034,7 @@
         <v>83</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>83</v>
@@ -14976,10 +15043,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -14990,21 +15057,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>83</v>
@@ -15013,19 +15080,19 @@
         <v>83</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15063,31 +15130,31 @@
         <v>83</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>83</v>
@@ -15096,10 +15163,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15110,10 +15177,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15136,26 +15203,24 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>554</v>
+        <v>83</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>83</v>
@@ -15197,7 +15262,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15218,10 +15283,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15232,10 +15297,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15258,18 +15323,18 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
       </c>
@@ -15317,7 +15382,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15338,10 +15403,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15352,10 +15417,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15363,7 +15428,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>94</v>
@@ -15378,17 +15443,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O110" t="s" s="2">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15437,7 +15504,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15458,10 +15525,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15472,12 +15539,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C111" s="2"/>
+      <c r="C111" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
       </c>
@@ -15498,17 +15567,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>259</v>
+        <v>568</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O111" t="s" s="2">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15533,13 +15604,11 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>83</v>
+        <v>569</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15557,13 +15626,13 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
@@ -15578,10 +15647,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15592,10 +15661,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15615,23 +15684,19 @@
         <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
@@ -15679,7 +15744,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15691,7 +15756,7 @@
         <v>83</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>83</v>
@@ -15700,10 +15765,10 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15714,23 +15779,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C113" t="s" s="2">
         <v>560</v>
       </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
@@ -15739,23 +15802,21 @@
         <v>83</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>561</v>
+        <v>215</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>83</v>
       </c>
@@ -15779,29 +15840,31 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>562</v>
+        <v>83</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15813,7 +15876,7 @@
         <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>83</v>
@@ -15822,10 +15885,10 @@
         <v>83</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15836,10 +15899,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15847,7 +15910,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>94</v>
@@ -15859,25 +15922,29 @@
         <v>83</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>205</v>
+        <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>83</v>
+        <v>573</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -15919,7 +15986,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15931,7 +15998,7 @@
         <v>83</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>83</v>
@@ -15940,10 +16007,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -15954,21 +16021,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>83</v>
@@ -15977,19 +16044,19 @@
         <v>83</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16027,31 +16094,31 @@
         <v>83</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>83</v>
@@ -16060,10 +16127,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16074,10 +16141,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16100,26 +16167,24 @@
         <v>95</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>566</v>
+        <v>83</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>83</v>
@@ -16161,7 +16226,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16182,10 +16247,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16196,10 +16261,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16222,18 +16287,18 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
       </c>
@@ -16281,7 +16346,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16302,10 +16367,10 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16316,10 +16381,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16327,7 +16392,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>94</v>
@@ -16342,17 +16407,19 @@
         <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O118" t="s" s="2">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16401,7 +16468,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16422,10 +16489,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16436,12 +16503,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16462,17 +16531,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>259</v>
+        <v>580</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O119" t="s" s="2">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
@@ -16497,13 +16568,11 @@
         <v>83</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16521,13 +16590,13 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>83</v>
@@ -16542,10 +16611,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16556,10 +16625,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16579,23 +16648,19 @@
         <v>83</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -16643,7 +16708,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16655,7 +16720,7 @@
         <v>83</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>83</v>
@@ -16664,10 +16729,10 @@
         <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -16678,21 +16743,21 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>83</v>
@@ -16701,23 +16766,21 @@
         <v>83</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>278</v>
+        <v>215</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -16753,31 +16816,31 @@
         <v>83</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>83</v>
@@ -16786,10 +16849,10 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>283</v>
+        <v>212</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -16800,10 +16863,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16811,7 +16874,7 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>94</v>
@@ -16826,26 +16889,26 @@
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>573</v>
+        <v>108</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>574</v>
+        <v>235</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>575</v>
+        <v>236</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>576</v>
+        <v>237</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>398</v>
+        <v>238</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16887,7 +16950,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>572</v>
+        <v>240</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16905,27 +16968,27 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>401</v>
+        <v>241</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>402</v>
+        <v>242</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16945,23 +17008,21 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>579</v>
+        <v>245</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>580</v>
+        <v>246</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>83</v>
       </c>
@@ -16985,13 +17046,13 @@
         <v>83</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>83</v>
@@ -17009,7 +17070,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>578</v>
+        <v>248</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17018,7 +17079,7 @@
         <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>106</v>
@@ -17030,10 +17091,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>412</v>
+        <v>250</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17044,21 +17105,21 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>83</v>
@@ -17067,22 +17128,20 @@
         <v>83</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>583</v>
+        <v>253</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>586</v>
+        <v>255</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17107,13 +17166,13 @@
         <v>83</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>83</v>
@@ -17131,13 +17190,13 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>582</v>
+        <v>257</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>83</v>
@@ -17149,27 +17208,27 @@
         <v>83</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>420</v>
+        <v>258</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>421</v>
+        <v>259</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>587</v>
+        <v>564</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17180,7 +17239,7 @@
         <v>81</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>83</v>
@@ -17189,22 +17248,20 @@
         <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>588</v>
+        <v>262</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>591</v>
+        <v>264</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>83</v>
@@ -17253,13 +17310,13 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>587</v>
+        <v>265</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>83</v>
@@ -17274,15 +17331,747 @@
         <v>83</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>466</v>
+        <v>266</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>467</v>
+        <v>267</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP125" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP131" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -525,8 +525,7 @@
 </t>
   </si>
   <si>
-    <t>実施されるプラン、提案、依頼  
-【JP Core仕様】未使用</t>
+    <t>実施されるプラン、提案、依頼  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>本プロファイル（特定の歯の有無・状態）は口腔診査レポートに紐付く前提のため、本プロファイル特有の定義はしない。</t>
@@ -555,8 +554,7 @@
 </t>
   </si>
   <si>
-    <t>参照されるイベントの一部分  
-【JP Core仕様】未使用</t>
+    <t>参照されるイベントの一部分 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>ObservationをEncounterにencounter要素を使ってリンクする。もうひとつ別のObservationを参照することについては、以降にあるt [Notes](observation.html#obsgrouping)　をガイダンスとして参照のこと。</t>
@@ -574,8 +572,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>結果の状態  
-【JP Core仕様】ステータス</t>
+    <t>結果の状態 【JP Core仕様】ステータス</t>
   </si>
   <si>
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
@@ -618,16 +615,15 @@
 </t>
   </si>
   <si>
-    <t>Observationの種類（タイプ）の分類
-【JP Core仕様】以下を指定する。
+    <t>Observationの種類（タイプ）の分類</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】以下を指定する。
 第1コード：exam
 第2コード：LP89803-8 （Dental）
 第3コード：DO-1-03 （MissingToothCondition）</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
-  </si>
-  <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
@@ -919,6 +915,9 @@
   </si>
   <si>
     <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -5574,7 +5573,7 @@
         <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>194</v>
@@ -5661,7 +5660,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -5779,7 +5778,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -5899,7 +5898,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6021,7 +6020,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6139,7 +6138,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6259,7 +6258,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6304,7 +6303,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6381,7 +6380,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>244</v>
@@ -6501,7 +6500,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>252</v>
@@ -6544,7 +6543,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6621,7 +6620,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -6741,7 +6740,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -6863,7 +6862,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -6985,13 +6984,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7016,13 +7015,13 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>194</v>
@@ -7054,7 +7053,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7107,7 +7106,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>207</v>
@@ -7225,7 +7224,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>214</v>
@@ -7345,7 +7344,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>220</v>
@@ -7467,7 +7466,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>230</v>
@@ -7585,7 +7584,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>232</v>
@@ -7705,7 +7704,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>234</v>
@@ -7750,7 +7749,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7827,7 +7826,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>244</v>
@@ -7947,7 +7946,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>252</v>
@@ -7990,7 +7989,7 @@
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8067,7 +8066,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8187,7 +8186,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8309,7 +8308,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8431,14 +8430,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8460,16 +8459,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8494,13 +8493,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8518,7 +8517,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8533,30 +8532,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8671,10 +8670,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8791,10 +8790,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8820,10 +8819,10 @@
         <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>224</v>
@@ -8913,10 +8912,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9031,10 +9030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9151,10 +9150,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9196,7 +9195,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9273,10 +9272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9393,10 +9392,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9436,7 +9435,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9513,10 +9512,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9559,7 +9558,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9633,10 +9632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9755,10 +9754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9877,10 +9876,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9903,19 +9902,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9964,7 +9963,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9979,19 +9978,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9999,10 +9998,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10025,16 +10024,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10084,7 +10083,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10105,13 +10104,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10119,14 +10118,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10145,19 +10144,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10206,7 +10205,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10221,19 +10220,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10241,14 +10240,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10267,19 +10266,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10328,7 +10327,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10343,19 +10342,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10363,10 +10362,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10389,16 +10388,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10448,7 +10447,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10469,13 +10468,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10483,10 +10482,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10509,19 +10508,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10570,7 +10569,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10585,19 +10584,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10605,10 +10604,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10634,16 +10633,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10692,7 +10691,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10701,7 +10700,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10710,27 +10709,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10756,16 +10755,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10790,13 +10789,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10814,7 +10813,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10823,7 +10822,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10838,7 +10837,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10849,14 +10848,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10878,16 +10877,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10912,13 +10911,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10936,7 +10935,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10954,27 +10953,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10997,19 +10996,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11058,7 +11057,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11079,10 +11078,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11093,10 +11092,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11122,13 +11121,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11158,7 +11157,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11176,7 +11175,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11194,27 +11193,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11329,10 +11328,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11449,13 +11448,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11477,13 +11476,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11569,13 +11568,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
@@ -11597,13 +11596,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11689,10 +11688,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11811,10 +11810,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11933,10 +11932,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11962,16 +11961,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11996,13 +11995,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12020,7 +12019,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12041,10 +12040,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12055,10 +12054,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12081,16 +12080,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12140,7 +12139,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12158,27 +12157,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12201,16 +12200,16 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12260,7 +12259,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12278,27 +12277,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12321,19 +12320,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12382,7 +12381,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12394,7 +12393,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12403,10 +12402,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12417,10 +12416,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12535,10 +12534,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12655,14 +12654,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12684,10 +12683,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -12742,7 +12741,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12777,10 +12776,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12803,13 +12802,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12860,7 +12859,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12869,7 +12868,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12881,10 +12880,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12895,10 +12894,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12921,13 +12920,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12978,7 +12977,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12987,7 +12986,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12999,10 +12998,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13013,10 +13012,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13042,16 +13041,16 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13079,10 +13078,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13100,7 +13099,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13118,13 +13117,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13135,10 +13134,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13164,16 +13163,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13198,13 +13197,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13222,7 +13221,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13240,13 +13239,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13257,10 +13256,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13283,17 +13282,17 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13342,7 +13341,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13366,7 +13365,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13377,10 +13376,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13406,10 +13405,10 @@
         <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13460,7 +13459,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13481,10 +13480,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13495,10 +13494,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13509,7 +13508,7 @@
         <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13521,16 +13520,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13580,7 +13579,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13601,10 +13600,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13615,10 +13614,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13641,16 +13640,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13700,7 +13699,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13721,10 +13720,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13735,10 +13734,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13761,19 +13760,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13822,7 +13821,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13843,10 +13842,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13857,10 +13856,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13975,10 +13974,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14095,14 +14094,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14124,10 +14123,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
@@ -14182,7 +14181,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14217,10 +14216,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14246,16 +14245,16 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14280,13 +14279,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14304,7 +14303,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14322,16 +14321,16 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14339,10 +14338,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14457,10 +14456,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14577,10 +14576,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14652,7 +14651,7 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -14697,10 +14696,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14815,10 +14814,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14935,10 +14934,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15057,10 +15056,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15177,10 +15176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15297,10 +15296,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15417,10 +15416,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15539,13 +15538,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15570,10 +15569,10 @@
         <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>224</v>
@@ -15608,7 +15607,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15661,10 +15660,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15779,10 +15778,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15899,10 +15898,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15944,7 +15943,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -16021,10 +16020,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16141,10 +16140,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16261,10 +16260,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16381,10 +16380,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16503,13 +16502,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16534,10 +16533,10 @@
         <v>221</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>224</v>
@@ -16572,7 +16571,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16625,10 +16624,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16743,10 +16742,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16863,10 +16862,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16908,7 +16907,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16985,10 +16984,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17105,10 +17104,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17225,10 +17224,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17345,10 +17344,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17467,10 +17466,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17589,10 +17588,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17615,19 +17614,19 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -17676,7 +17675,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17694,27 +17693,27 @@
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17740,16 +17739,16 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17774,13 +17773,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -17798,7 +17797,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -17807,7 +17806,7 @@
         <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -17822,7 +17821,7 @@
         <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17833,14 +17832,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17862,16 +17861,16 @@
         <v>191</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -17896,13 +17895,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -17920,7 +17919,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -17938,27 +17937,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17984,16 +17983,16 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18042,7 +18041,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18063,10 +18062,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-24</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -630,7 +630,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1032,7 +1032,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1127,7 +1127,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1300,7 +1300,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1329,7 +1329,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1446,7 +1446,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1483,7 +1483,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1558,7 +1558,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1608,7 +1608,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1641,7 +1641,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -633,7 +633,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -920,6 +920,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP89803-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -936,9 +944,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -1073,6 +1078,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding.version</t>
@@ -5586,7 +5594,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5660,7 +5668,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -5778,7 +5786,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -5898,7 +5906,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6020,7 +6028,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6138,7 +6146,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6258,7 +6266,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6303,7 +6311,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -9195,7 +9203,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9272,10 +9280,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9392,10 +9400,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9435,7 +9443,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9512,10 +9520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9558,7 +9566,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9632,10 +9640,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9754,10 +9762,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9876,10 +9884,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9902,19 +9910,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9963,7 +9971,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9978,19 +9986,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9998,10 +10006,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10024,16 +10032,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10083,7 +10091,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10107,10 +10115,10 @@
         <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10118,14 +10126,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10144,19 +10152,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10205,7 +10213,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10220,19 +10228,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10240,14 +10248,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10266,19 +10274,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10327,7 +10335,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10342,19 +10350,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10362,10 +10370,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10388,16 +10396,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10447,7 +10455,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10468,13 +10476,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10482,10 +10490,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10508,19 +10516,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10569,7 +10577,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10584,19 +10592,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10604,10 +10612,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10633,16 +10641,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10691,7 +10699,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10700,7 +10708,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10709,27 +10717,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10755,16 +10763,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10789,13 +10797,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10813,7 +10821,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10822,7 +10830,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10837,7 +10845,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10848,14 +10856,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10877,16 +10885,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10911,13 +10919,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10935,7 +10943,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10953,27 +10961,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10996,19 +11004,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11057,7 +11065,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11078,10 +11086,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11092,10 +11100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11121,13 +11129,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11157,7 +11165,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11175,7 +11183,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11193,27 +11201,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11328,10 +11336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11448,13 +11456,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11476,13 +11484,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11568,13 +11576,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
@@ -11596,13 +11604,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11688,10 +11696,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11810,10 +11818,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11932,10 +11940,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11961,16 +11969,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -11998,10 +12006,10 @@
         <v>326</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12019,7 +12027,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12040,10 +12048,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12054,10 +12062,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12080,16 +12088,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12139,7 +12147,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12157,27 +12165,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12200,16 +12208,16 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12259,7 +12267,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12277,27 +12285,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12320,19 +12328,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12381,7 +12389,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12393,7 +12401,7 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12402,10 +12410,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12416,10 +12424,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12534,10 +12542,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12654,14 +12662,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12683,10 +12691,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -12741,7 +12749,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12776,10 +12784,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12802,13 +12810,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12859,7 +12867,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12868,7 +12876,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12880,10 +12888,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12894,10 +12902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12920,13 +12928,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12977,7 +12985,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12986,7 +12994,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12998,10 +13006,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13012,10 +13020,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13041,16 +13049,16 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13078,10 +13086,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13099,7 +13107,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13117,13 +13125,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13134,10 +13142,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13163,16 +13171,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13200,10 +13208,10 @@
         <v>326</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13221,7 +13229,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13239,13 +13247,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13256,10 +13264,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13282,17 +13290,17 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13341,7 +13349,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13365,7 +13373,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13376,10 +13384,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13405,10 +13413,10 @@
         <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13459,7 +13467,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13480,10 +13488,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13494,10 +13502,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13520,16 +13528,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13579,7 +13587,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13600,10 +13608,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13614,10 +13622,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13640,16 +13648,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13699,7 +13707,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13720,10 +13728,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13734,10 +13742,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13760,19 +13768,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13821,7 +13829,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13842,10 +13850,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13856,10 +13864,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13974,10 +13982,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14094,14 +14102,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14123,10 +14131,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
@@ -14181,7 +14189,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14216,10 +14224,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14245,13 +14253,13 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>325</v>
@@ -14303,7 +14311,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14321,7 +14329,7 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>331</v>
@@ -14338,10 +14346,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14456,10 +14464,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14576,10 +14584,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14651,7 +14659,7 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -14696,10 +14704,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14814,10 +14822,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14934,10 +14942,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15056,10 +15064,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15176,10 +15184,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15296,10 +15304,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15416,10 +15424,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15538,13 +15546,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15569,10 +15577,10 @@
         <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>224</v>
@@ -15607,7 +15615,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15660,10 +15668,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15778,10 +15786,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15898,10 +15906,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15943,7 +15951,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -16020,10 +16028,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16140,10 +16148,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16260,10 +16268,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16380,10 +16388,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16502,13 +16510,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16533,10 +16541,10 @@
         <v>221</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>224</v>
@@ -16571,7 +16579,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16624,10 +16632,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16742,10 +16750,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16862,10 +16870,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16907,7 +16915,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16984,10 +16992,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17104,10 +17112,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17224,10 +17232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17344,10 +17352,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17466,10 +17474,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17588,10 +17596,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17614,19 +17622,19 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -17675,7 +17683,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17693,27 +17701,27 @@
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17739,16 +17747,16 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17773,13 +17781,13 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>83</v>
@@ -17797,7 +17805,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -17806,7 +17814,7 @@
         <v>94</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -17821,7 +17829,7 @@
         <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17832,14 +17840,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17861,16 +17869,16 @@
         <v>191</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -17895,13 +17903,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -17919,7 +17927,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -17937,27 +17945,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17983,16 +17991,16 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18041,7 +18049,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18062,10 +18070,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -1114,7 +1114,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1159,7 +1159,7 @@
 </t>
   </si>
   <si>
-    <t>このobservationが行われるヘルスケアイベント</t>
+    <t>このobservationが行われる診療イベント</t>
   </si>
   <si>
     <t>例：診療、歯科検診、身元不明者調査</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -658,6 +658,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="exam"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -812,9 +820,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -952,9 +957,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>LP89803-8</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -973,6 +975,14 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS"/&gt;
+    &lt;code value="DO-1-03"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
@@ -994,16 +1004,10 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
-  </si>
-  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
-  </si>
-  <si>
-    <t>DO-1-03</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
@@ -4148,7 +4152,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4167,7 +4171,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4220,10 +4224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4246,13 +4250,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4303,7 +4307,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4327,7 +4331,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4338,10 +4342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4370,7 +4374,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4411,10 +4415,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4423,7 +4427,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4447,7 +4451,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4458,10 +4462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4484,19 +4488,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4545,7 +4549,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4566,10 +4570,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4580,10 +4584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4606,13 +4610,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4663,7 +4667,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4687,7 +4691,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4698,10 +4702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4730,7 +4734,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4771,10 +4775,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4783,7 +4787,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4807,7 +4811,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4818,10 +4822,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4847,23 +4851,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4905,7 +4909,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4926,10 +4930,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4940,10 +4944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4966,16 +4970,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5025,7 +5029,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5046,10 +5050,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5060,10 +5064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5089,21 +5093,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5206,7 +5210,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -5448,7 +5452,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>280</v>
@@ -5671,7 +5675,7 @@
         <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5694,13 +5698,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5751,7 +5755,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5775,7 +5779,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5789,7 +5793,7 @@
         <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5818,7 +5822,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5859,10 +5863,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5871,7 +5875,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5895,7 +5899,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5909,7 +5913,7 @@
         <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5932,19 +5936,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5993,7 +5997,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6014,10 +6018,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6031,7 +6035,7 @@
         <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6054,13 +6058,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6111,7 +6115,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6135,7 +6139,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6149,7 +6153,7 @@
         <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6178,7 +6182,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6219,10 +6223,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6231,7 +6235,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6255,7 +6259,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6269,7 +6273,7 @@
         <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6295,16 +6299,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6353,7 +6357,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6374,10 +6378,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6391,7 +6395,7 @@
         <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6414,16 +6418,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6473,7 +6477,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6494,10 +6498,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6511,7 +6515,7 @@
         <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6537,21 +6541,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6628,7 +6632,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -6654,7 +6658,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>262</v>
@@ -6748,7 +6752,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -6870,7 +6874,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -6896,7 +6900,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>280</v>
@@ -6992,13 +6996,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7023,10 +7027,10 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>290</v>
@@ -7042,7 +7046,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -7117,7 +7121,7 @@
         <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7140,13 +7144,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7197,7 +7201,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7221,7 +7225,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7235,7 +7239,7 @@
         <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7264,7 +7268,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7305,10 +7309,10 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
@@ -7317,7 +7321,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7341,7 +7345,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7355,7 +7359,7 @@
         <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7378,19 +7382,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7439,7 +7443,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7460,10 +7464,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7477,7 +7481,7 @@
         <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7500,13 +7504,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7557,7 +7561,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7581,7 +7585,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7595,7 +7599,7 @@
         <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7624,7 +7628,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7665,10 +7669,10 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
@@ -7677,7 +7681,7 @@
         <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7701,7 +7705,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7715,7 +7719,7 @@
         <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7741,23 +7745,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7799,7 +7803,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7820,10 +7824,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7834,10 +7838,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7860,16 +7864,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7919,7 +7923,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7940,10 +7944,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7954,10 +7958,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7983,21 +7987,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8074,7 +8078,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8100,7 +8104,7 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>262</v>
@@ -8194,7 +8198,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8316,7 +8320,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8342,7 +8346,7 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>280</v>
@@ -8438,14 +8442,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8467,16 +8471,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8501,14 +8505,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8525,7 +8529,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8540,30 +8544,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8586,13 +8590,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8643,7 +8647,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8667,7 +8671,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8678,10 +8682,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8710,7 +8714,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8751,10 +8755,10 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
@@ -8763,7 +8767,7 @@
         <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8787,7 +8791,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8798,10 +8802,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8824,19 +8828,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8885,7 +8889,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8906,10 +8910,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8920,10 +8924,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8946,13 +8950,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9003,7 +9007,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9027,7 +9031,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9038,10 +9042,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9070,7 +9074,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9111,10 +9115,10 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
@@ -9123,7 +9127,7 @@
         <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9147,7 +9151,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9158,10 +9162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9187,23 +9191,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9245,7 +9249,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9266,10 +9270,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9280,10 +9284,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9306,16 +9310,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9365,7 +9369,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9386,10 +9390,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9400,10 +9404,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9429,21 +9433,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9520,10 +9524,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9546,7 +9550,7 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>262</v>
@@ -9566,7 +9570,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9640,10 +9644,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9762,10 +9766,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9788,7 +9792,7 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>280</v>
@@ -9884,10 +9888,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9910,19 +9914,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9971,7 +9975,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9986,19 +9990,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10006,10 +10010,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10032,16 +10036,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10091,7 +10095,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10112,13 +10116,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10126,14 +10130,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10152,19 +10156,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10213,7 +10217,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10228,19 +10232,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10248,14 +10252,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10274,19 +10278,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10335,7 +10339,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10350,19 +10354,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10370,10 +10374,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10396,16 +10400,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10455,7 +10459,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10476,13 +10480,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10490,10 +10494,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10516,19 +10520,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10577,7 +10581,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10592,19 +10596,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10612,10 +10616,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10641,16 +10645,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10699,7 +10703,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10708,7 +10712,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10717,27 +10721,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10763,16 +10767,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10797,40 +10801,40 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10845,7 +10849,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10856,14 +10860,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10885,16 +10889,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10919,13 +10923,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10943,7 +10947,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10961,27 +10965,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>428</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11004,19 +11008,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11065,7 +11069,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11086,10 +11090,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11100,10 +11104,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11129,13 +11133,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11165,7 +11169,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11183,7 +11187,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11201,27 +11205,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11244,13 +11248,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11301,7 +11305,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11325,7 +11329,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11336,10 +11340,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11368,7 +11372,7 @@
         <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11409,10 +11413,10 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
@@ -11421,7 +11425,7 @@
         <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11445,7 +11449,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11456,13 +11460,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11484,13 +11488,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11541,7 +11545,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11576,13 +11580,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
@@ -11604,13 +11608,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11661,7 +11665,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11696,10 +11700,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11722,19 +11726,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11783,7 +11787,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11804,10 +11808,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11818,10 +11822,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11844,7 +11848,7 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>280</v>
@@ -11940,10 +11944,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11969,16 +11973,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O81" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12003,13 +12007,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12027,7 +12031,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12048,10 +12052,10 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12062,10 +12066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12088,16 +12092,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12147,7 +12151,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12165,27 +12169,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12208,16 +12212,16 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12267,7 +12271,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12285,27 +12289,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="AO83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12328,19 +12332,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12389,7 +12393,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12401,19 +12405,19 @@
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12424,10 +12428,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12450,13 +12454,13 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12507,7 +12511,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12531,7 +12535,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12542,10 +12546,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12574,7 +12578,7 @@
         <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -12627,7 +12631,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12651,7 +12655,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12662,14 +12666,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12691,10 +12695,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -12749,7 +12753,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12784,10 +12788,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12810,13 +12814,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12867,7 +12871,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12876,7 +12880,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12888,10 +12892,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12902,10 +12906,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12928,13 +12932,13 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12985,7 +12989,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12994,7 +12998,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13006,10 +13010,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13020,10 +13024,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13049,16 +13053,16 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13086,10 +13090,10 @@
         <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13107,7 +13111,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13125,13 +13129,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13142,10 +13146,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13171,16 +13175,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13205,13 +13209,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13229,7 +13233,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13247,13 +13251,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13264,10 +13268,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13290,17 +13294,17 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13349,7 +13353,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13373,7 +13377,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13384,10 +13388,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13410,13 +13414,13 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13467,7 +13471,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13488,10 +13492,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13502,10 +13506,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13528,16 +13532,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13587,7 +13591,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13608,10 +13612,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13622,10 +13626,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13648,16 +13652,16 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13707,7 +13711,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13728,10 +13732,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13742,10 +13746,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13768,19 +13772,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13829,7 +13833,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13850,10 +13854,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13864,10 +13868,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13890,13 +13894,13 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13947,7 +13951,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13971,7 +13975,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13982,10 +13986,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14014,7 +14018,7 @@
         <v>141</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
@@ -14067,7 +14071,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14091,7 +14095,7 @@
         <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14102,14 +14106,14 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14131,10 +14135,10 @@
         <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>143</v>
@@ -14189,7 +14193,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14224,10 +14228,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14253,16 +14257,16 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>555</v>
-      </c>
       <c r="O100" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14287,14 +14291,14 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y100" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14311,7 +14315,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>94</v>
@@ -14329,16 +14333,16 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14346,10 +14350,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14372,13 +14376,13 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14429,7 +14433,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14453,7 +14457,7 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14464,10 +14468,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14496,7 +14500,7 @@
         <v>141</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>143</v>
@@ -14537,10 +14541,10 @@
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
@@ -14549,7 +14553,7 @@
         <v>198</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14573,7 +14577,7 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14584,10 +14588,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14610,19 +14614,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14659,7 +14663,7 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -14669,7 +14673,7 @@
         <v>198</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14690,10 +14694,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14704,10 +14708,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14730,13 +14734,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14787,7 +14791,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14811,7 +14815,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14822,10 +14826,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14854,7 +14858,7 @@
         <v>141</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>143</v>
@@ -14895,10 +14899,10 @@
         <v>83</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
@@ -14907,7 +14911,7 @@
         <v>198</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14931,7 +14935,7 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14942,10 +14946,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14971,16 +14975,16 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15029,7 +15033,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15050,10 +15054,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15064,10 +15068,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15090,16 +15094,16 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15149,7 +15153,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15170,10 +15174,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15184,10 +15188,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15213,14 +15217,14 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15304,10 +15308,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15330,7 +15334,7 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>262</v>
@@ -15424,10 +15428,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15546,13 +15550,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
@@ -15574,19 +15578,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15615,7 +15619,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15633,7 +15637,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15654,10 +15658,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15668,10 +15672,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15694,13 +15698,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15751,7 +15755,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15775,7 +15779,7 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15786,10 +15790,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15818,7 +15822,7 @@
         <v>141</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15859,10 +15863,10 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
@@ -15871,7 +15875,7 @@
         <v>198</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15895,7 +15899,7 @@
         <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15906,10 +15910,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15935,23 +15939,23 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -15993,7 +15997,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16014,10 +16018,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -16028,10 +16032,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16054,16 +16058,16 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16113,7 +16117,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16134,10 +16138,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16148,10 +16152,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16177,14 +16181,14 @@
         <v>114</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16268,10 +16272,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16294,7 +16298,7 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>262</v>
@@ -16388,10 +16392,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16510,13 +16514,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16538,19 +16542,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
@@ -16579,7 +16583,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16597,7 +16601,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16618,10 +16622,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16632,10 +16636,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16658,13 +16662,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16715,7 +16719,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16739,7 +16743,7 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -16750,10 +16754,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16782,7 +16786,7 @@
         <v>141</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>143</v>
@@ -16823,10 +16827,10 @@
         <v>83</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>83</v>
@@ -16835,7 +16839,7 @@
         <v>198</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -16859,7 +16863,7 @@
         <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -16870,10 +16874,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16899,23 +16903,23 @@
         <v>108</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16957,7 +16961,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -16978,10 +16982,10 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -16992,10 +16996,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17018,16 +17022,16 @@
         <v>95</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17077,7 +17081,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17098,10 +17102,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17112,10 +17116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17141,14 +17145,14 @@
         <v>114</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>83</v>
@@ -17232,10 +17236,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17258,7 +17262,7 @@
         <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>262</v>
@@ -17352,10 +17356,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17474,10 +17478,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17500,7 +17504,7 @@
         <v>95</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>280</v>
@@ -17596,10 +17600,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17622,19 +17626,19 @@
         <v>95</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M128" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="O128" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
@@ -17683,7 +17687,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -17701,27 +17705,27 @@
         <v>83</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP128" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17747,16 +17751,16 @@
         <v>191</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>602</v>
-      </c>
       <c r="O129" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -17781,40 +17785,40 @@
         <v>83</v>
       </c>
       <c r="X129" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z129" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Y129" t="s" s="2">
+      <c r="AA129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI129" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>106</v>
@@ -17829,7 +17833,7 @@
         <v>137</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -17840,14 +17844,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17869,16 +17873,16 @@
         <v>191</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -17903,13 +17907,13 @@
         <v>83</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>83</v>
@@ -17927,7 +17931,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -17945,27 +17949,27 @@
         <v>83</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM130" t="s" s="2">
+      <c r="AO130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP130" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>428</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17991,16 +17995,16 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18049,7 +18053,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18070,10 +18074,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -550,7 +550,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1118,7 +1118,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
+    <t>原則subjectを記述すべきだが、対象患者が不明なデバイス観察のケースを考慮し、cardinalityは0..1とする。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1146,7 +1146,7 @@
     <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。  【JP Core仕様】未使用</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1731,7 +1731,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
